--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-30).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-30).xlsx
@@ -912,30 +912,30 @@
   </si>
   <si>
     <t>214
-180</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>R$ 1.694.946,80</t>
-  </si>
-  <si>
-    <t>R$ 8.920,77
-R$ 9.021,24</t>
-  </si>
-  <si>
-    <t>(7.1%)
-(5.8%)</t>
-  </si>
-  <si>
-    <t>99.1</t>
+181</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>R$ 1.706.520,01</t>
+  </si>
+  <si>
+    <t>R$ 8.934,66
+R$ 9.035,34</t>
+  </si>
+  <si>
+    <t>(7.0%)
+(5.7%)</t>
+  </si>
+  <si>
+    <t>99.2</t>
   </si>
   <si>
     <t>(9.1%)</t>
   </si>
   <si>
-    <t>24.6%</t>
+    <t>24.7%</t>
   </si>
   <si>
     <t>(13.3%)</t>
@@ -950,10 +950,10 @@
     <t>29.9</t>
   </si>
   <si>
-    <t>61.6%</t>
-  </si>
-  <si>
-    <t>15.6%</t>
+    <t>61.5%</t>
+  </si>
+  <si>
+    <t>15.5%</t>
   </si>
   <si>
     <t>7.0</t>
@@ -968,13 +968,13 @@
     <t>21.4</t>
   </si>
   <si>
-    <t>63.4%</t>
-  </si>
-  <si>
-    <t>-R$ 47.604,87</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>63.5%</t>
+  </si>
+  <si>
+    <t>-R$ 47.666,77</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -8764,7 +8764,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8800,27 +8800,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>11573.209999999999</v>
+      </c>
+      <c r="P58" s="5">
+        <v>11573.209999999999</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.036238592897153366</v>
+      </c>
+      <c r="R58" s="7">
+        <v>132</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.043478260869565188</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.2822159625549005</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.070578119640099857</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.011346549487998576</v>
+      </c>
+      <c r="W58" s="6">
+        <v>0.00020357359799053157</v>
+      </c>
+      <c r="X58" s="8">
+        <v>25.116012745098036</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.45098039215686275</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>4.4328162790697672</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>6.2412544554455449</v>
+      </c>
       <c r="AC58" s="8">
         <v>10.888966</v>
       </c>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>17.740196078431371</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.77450980392156865</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-61.899999999999999</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -15415,7 +15449,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15804,7 +15838,7 @@
         <v>-85.700000000000003</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16977,7 +17011,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17370,7 +17404,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18547,7 +18581,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20865,7 +20899,7 @@
         <v>-396.19999999999999</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -22149,7 +22183,7 @@
         <v>-308.23000000000002</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -28312,7 +28346,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-30).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-30).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-181</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>R$ 1.706.520,01</t>
-  </si>
-  <si>
-    <t>R$ 8.934,66
-R$ 9.035,34</t>
-  </si>
-  <si>
-    <t>(7.0%)
-(5.7%)</t>
-  </si>
-  <si>
-    <t>99.2</t>
-  </si>
-  <si>
-    <t>(9.1%)</t>
+184</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>R$ 1.722.919,10</t>
+  </si>
+  <si>
+    <t>R$ 8.881,03
+R$ 8.977,15</t>
+  </si>
+  <si>
+    <t>(7.2%)
+(5.9%)</t>
+  </si>
+  <si>
+    <t>98.5</t>
+  </si>
+  <si>
+    <t>(9.3%)</t>
   </si>
   <si>
     <t>24.7%</t>
   </si>
   <si>
-    <t>(13.3%)</t>
+    <t>(13.2%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -947,34 +947,34 @@
     <t>0.7%</t>
   </si>
   <si>
-    <t>29.9</t>
+    <t>30.1</t>
   </si>
   <si>
     <t>61.5%</t>
   </si>
   <si>
-    <t>15.5%</t>
+    <t>15.8%</t>
   </si>
   <si>
     <t>7.0</t>
   </si>
   <si>
-    <t>7.8</t>
-  </si>
-  <si>
-    <t>14.8</t>
-  </si>
-  <si>
-    <t>21.4</t>
-  </si>
-  <si>
-    <t>63.5%</t>
-  </si>
-  <si>
-    <t>-R$ 47.666,77</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>7.9</t>
+  </si>
+  <si>
+    <t>14.9</t>
+  </si>
+  <si>
+    <t>21.5</t>
+  </si>
+  <si>
+    <t>63.2%</t>
+  </si>
+  <si>
+    <t>-R$ 47.791,77</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -5966,7 +5966,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -6002,25 +6002,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>5525.8699999999999</v>
+      </c>
+      <c r="P36" s="5">
+        <v>5525.8699999999999</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.12152101579105512</v>
+      </c>
+      <c r="R36" s="7">
+        <v>66</v>
+      </c>
+      <c r="S36" s="6">
+        <v>-0.070422535211267623</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.48315852526389513</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.17786723176621963</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.10614400990251309</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.066380135616654026</v>
+      </c>
+      <c r="X36" s="8">
+        <v>68.066964285714292</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.8035714285714286</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>11.970454545454544</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>29.863332727272731</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>42.048127999999998</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>48.508630357142856</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.089285714285714288</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7887,7 +7923,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7923,25 +7959,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>685.29999999999995</v>
+      </c>
+      <c r="P51" s="5">
+        <v>685.29999999999995</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.60242501595405229</v>
+      </c>
+      <c r="R51" s="7">
+        <v>7</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.63157894736842102</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.35596089303954476</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.053332846928352551</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.13346125784328033</v>
+      </c>
+      <c r="X51" s="8">
+        <v>36.975000000000001</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>5.9571428571428573</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>17.029174999999999</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>26.120832</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>33.024999999999999</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.25</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12622,7 +12694,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12661,7 +12733,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12695,25 +12767,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>10187.92</v>
+      </c>
+      <c r="P89" s="5">
+        <v>10187.92</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.21538498268334594</v>
+      </c>
+      <c r="R89" s="7">
+        <v>88</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.3529411764705882</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.12572467196444417</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.17748638583734463</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.019834470627959386</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0078732459618842711</v>
+      </c>
+      <c r="X89" s="8">
+        <v>32.49583333333333</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>8.5537875000000003</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>7.1205680851063828</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>23.25</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.375</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>-125</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16749,7 +16855,7 @@
         <v>-186.69999999999999</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18712,7 +18818,7 @@
         <v>-857.60000000000002</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -21026,7 +21132,7 @@
         <v>-112.2</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
